--- a/xiuxian配置表/yunxing_params/平衡设计.xlsx
+++ b/xiuxian配置表/yunxing_params/平衡设计.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>foundation_points_per_level</t>
+          <t>zhuji_points_per_level</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>foundation_avg_gain</t>
+          <t>zhuji_avg_gain</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>foundation_points_per_level</t>
+          <t>zhuji_points_per_level</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>foundation_avg_gain</t>
+          <t>zhuji_avg_gain</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>[{"level":1,"id":"qi","name":"炼气"},{"level":10,"id":"foundation","name":"筑基"},{"level":20,"id":"core","name":"金丹"},{"level":30,"id":"nascent","name":"元婴"},{"level":40,"id":"transform","name":"化神"},{"level":50,"id":"void","name":"炼虚"},{"level":60,"id":"merge","name":"合体"},{"level":70,"id":"great","name":"大乘"},{"level":80,"id":"tribulation","name":"渡劫"}]</t>
+          <t>[{"level":1,"id":"lianqi","name":"炼气"},{"level":10,"id":"zhuji","name":"筑基"},{"level":20,"id":"jindan","name":"金丹"},{"level":30,"id":"yuanying","name":"元婴"},{"level":40,"id":"huashen","name":"化神"},{"level":50,"id":"lianxu","name":"炼虚"},{"level":60,"id":"heti","name":"合体"},{"level":70,"id":"dacheng","name":"大乘"},{"level":80,"id":"dujie","name":"渡劫"}]</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -1527,7 +1527,7 @@
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>qi_early</t>
+          <t>lianqi_early</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>qi_mature</t>
+          <t>lianqi_mature</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>foundation_early</t>
+          <t>zhuji_early</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>qi_mature_vs_foundation_normal_win_rate_max</t>
+          <t>lianqi_mature_vs_foundation_normal_win_rate_max</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -2515,12 +2515,12 @@
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>qi_normal</t>
+          <t>lianqi_normal</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2537,12 +2537,12 @@
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>qi_elite</t>
+          <t>lianqi_elite</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2559,12 +2559,12 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>foundation_normal</t>
+          <t>zhuji_normal</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3110,47 +3110,47 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -3227,47 +3227,47 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>{"1":"qi","2":"foundation","3":"core","4":"nascent","5":"transform","6":"void","7":"merge","8":"great","9":"tribulation"}</t>
+          <t>{"1":"lianqi","2":"zhuji","3":"jindan","4":"yuanying","5":"huashen","6":"lianxu","7":"heti","8":"dacheng","9":"dujie"}</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
@@ -3938,12 +3938,12 @@
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>炼气</t>
+          <t>练气</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
@@ -3968,7 +3968,7 @@
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -3998,7 +3998,7 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="10" ht="27" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
     <row r="12" ht="27" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -4178,7 +4178,7 @@
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
